--- a/data/trans_bre/P36BPD07_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P36BPD07_R-Clase-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 3,17</t>
+          <t>-5,36; 2,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 9,96</t>
+          <t>0,25; 9,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 3,53</t>
+          <t>-5,78; 3,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 13,13</t>
+          <t>0,32; 12,78</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,45</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 3,47</t>
+          <t>-6,64; 3,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 9,84</t>
+          <t>-1,51; 10,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 4,05</t>
+          <t>-7,48; 3,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 13,76</t>
+          <t>-1,97; 14,15</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-3,55</t>
+          <t>7,08</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,37%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 6,7</t>
+          <t>-5,99; 6,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 8,88</t>
+          <t>0,47; 13,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 7,96</t>
+          <t>-6,88; 7,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 12,58</t>
+          <t>0,84; 20,84</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,06</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 1,71</t>
+          <t>-4,88; 1,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 22,82</t>
+          <t>1,22; 8,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 2,09</t>
+          <t>-5,67; 1,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 33,66</t>
+          <t>1,7; 13,35</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,89</t>
+          <t>9,22</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 6,93</t>
+          <t>-1,01; 6,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 20,08</t>
+          <t>3,88; 14,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 8,47</t>
+          <t>-1,2; 8,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,01; 32,69</t>
+          <t>5,56; 23,13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,36; 27,62</t>
+          <t>16,19; 28,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 13,0</t>
+          <t>-4,21; 15,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,9; 45,48</t>
+          <t>22,33; 45,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 21,25</t>
+          <t>-5,66; 26,82</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,97</t>
+          <t>0,47; 3,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 9,02</t>
+          <t>2,96; 7,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,76</t>
+          <t>0,56; 4,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 12,44</t>
+          <t>4,06; 10,18</t>
         </is>
       </c>
     </row>
